--- a/reports/集团总公司_利润表_2025-06.xlsx
+++ b/reports/集团总公司_利润表_2025-06.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>226043476</v>
+        <v>246081132</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>171978995</v>
+        <v>186853534</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>971471791</v>
+        <v>1053010805</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>701213</v>
+        <v>904655</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3954394</v>
+        <v>5126918</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>607733</v>
+        <v>790469</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3430793</v>
+        <v>4485392</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>517544</v>
+        <v>666751</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2907852</v>
+        <v>3785281</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>474386</v>
+        <v>615412</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2675858</v>
+        <v>3492720</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>259020</v>
+        <v>338718</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1454778</v>
+        <v>1920116</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>206176</v>
+        <v>267188</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1164267</v>
+        <v>1512248</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>223277404</v>
+        <v>242497939</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>169212923</v>
+        <v>183270341</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>86887968</v>
+        <v>95332475</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>492470963</v>
+        <v>537687298</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1592177</v>
+        <v>2842530</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>9030625</v>
+        <v>15997960</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1435321</v>
+        <v>2068377</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>8152650</v>
+        <v>11637389</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>77596413</v>
+        <v>81732422</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>436519992</v>
+        <v>459990682</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1638603</v>
+        <v>2064597</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>9311666</v>
+        <v>11649427</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>722239</v>
+        <v>1030227</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4072785</v>
+        <v>5825681</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2562724</v>
+        <v>3084295</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>14546803</v>
+        <v>17481683</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1135727</v>
+        <v>1541141</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6396932</v>
+        <v>8738645</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>53894391</v>
+        <v>53618442</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>304377816</v>
+        <v>304299117</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>170090</v>
+        <v>169351</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1019593</v>
+        <v>1020234</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3262598</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>18507146</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2177207</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>12332922</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>163524554</v>
+        <v>185179921</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>131277076</v>
+        <v>138565222</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>103471476</v>
+        <v>110508972</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>583279952</v>
+        <v>623161783</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27805600</v>
+        <v>28056250</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>157737090</v>
+        <v>157729506</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5481366</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>30828569</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1754088</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>9869109</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1095543</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>6170851</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1312947</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>7407859</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>983065</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>5557389</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>654228</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>3705323</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>544357</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3087544</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3053581</v>
+        <v>3026316</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>17161465</v>
+        <v>17177560</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1431284</v>
+        <v>1424833</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>8085149</v>
+        <v>8096451</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3721204</v>
+        <v>3701673</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>20949008</v>
+        <v>20935032</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>23999220</v>
+        <v>23994016</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>135608385</v>
+        <v>135473710</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>351212</v>
+        <v>2945515</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2100249</v>
+        <v>16566782</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1122261</v>
+        <v>1121585</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>6721813</v>
+        <v>6713860</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1157458</v>
+        <v>1071416</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>6962650</v>
+        <v>6415270</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>120196</v>
+        <v>120396</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>720421</v>
+        <v>719342</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>478976</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2860183</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>959217</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>5397480</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>319045</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1908235</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>238958</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1431720</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>397587</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2386902</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1362669</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>7719426</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>211365</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1273192</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>158372</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>954719</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>263888</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1590706</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>184812</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1113060</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132159</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>794724</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105897</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>635565</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79562</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>476569</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>59752850</v>
+        <v>60646304</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>64480253</v>
+        <v>65120098</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>548180</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3083165</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>133031</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>794817</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>210022</v>
+        <v>210656</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1260268</v>
+        <v>1260219</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>59542828</v>
+        <v>60983828</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7115473</v>
+        <v>7101490</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>42589781</v>
+        <v>42634576</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>52427355</v>
+        <v>53882338</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>52427355</v>
+        <v>53882338</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>52427355</v>
+        <v>53882338</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>52427355</v>
+        <v>53882338</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>52427355</v>
+        <v>53882338</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
